--- a/company_data.xlsx
+++ b/company_data.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,40 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+    </font>
+    <font>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +66,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,162 +490,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Employee ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>E101</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Rahul</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="18" t="n">
         <v>50000</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>E102</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="18" t="n">
         <v>38000</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Vijayawada</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>E103</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Arun</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="18" t="n">
         <v>52000</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Banglore</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>E104</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Sneha</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="18" t="n">
         <v>48000</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Eluru</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>E105</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Kiran</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="18" t="n">
         <v>42000</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Tirupathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>EMPLOYEE DETAILS REPORT</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:E8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>